--- a/Chaya_Monitoring Matrix.xlsx
+++ b/Chaya_Monitoring Matrix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive - Chay-Ya Nepal\Desktop\ktm working project\emergency\Unicef dashboard\partner_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive - Chay-Ya Nepal\Desktop\ktm working project\emergency\rasuwa cynn dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DF75EE87-99EC-43D8-90A7-0EF6239A8299}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{560C1298-7F23-474F-BEF4-915A276A4330}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF75EE87-99EC-43D8-90A7-0EF6239A8299}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{0852B150-3F40-4BB5-A447-6A23EDAC7EC4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{337F1315-C639-4669-8235-F9C229A04F9D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
   <si>
     <t>Disaster Response Matrix - 2025</t>
   </si>
@@ -328,32 +328,6 @@
   </si>
   <si>
     <t># of children benefited</t>
-  </si>
-  <si>
-    <t>One district-level WASH cluster coordination meeting was conducted, and the District WASH Cluster was activated to strengthen coordination and facilitate an effective WASH response.</t>
-  </si>
-  <si>
-    <t>Technical staff were mobilized to Uttargaya, Gosainkunda, and Kalika Rural Municipalities to conduct field missions for needs and damage assessments.</t>
-  </si>
-  <si>
-    <t>A total of 78 people (48 at Sivalaya School and 30 at Nilkanda Holding Center) in Uttargaya Rural Municipality accessed a sufficient quantity and quality of water for drinking and domestic needs.</t>
-  </si>
-  <si>
-    <t>A total of 333 women and girls in Gosainkunda Rural Municipality–5, covering Sano-Barkhu, Brabal, Thulo-Barkhu, and Thulo-Shyfru, accessed menstrual hygiene management services.</t>
-  </si>
-  <si>
-    <t>A total of 9 children (5 at Sivalaya School and 4 at Nilkanda School Holding Center) in Uttargaya Rural Municipality accessed safe and appropriate WASH facilities and hygiene services.</t>
-  </si>
-  <si>
-    <t>In Gosainkunda Rural Municipality–5, covering Sano-Barkhu, Brabal, Thulo-Barkhu, and Thulo-Shyfru, hygiene promotion and hand hygiene sessions incorporating SBC interventions were conducted during the distribution of WASH supplies.
-In addition, 48 people at Sivalaya School and 30 people at Nilkanda Holding Center in Uttargaya Rural Municipality, a total of 78 people, participated in hygiene promotion activities. One male and one female community volunteer mobilized to conduct these activities regularly.
-These activities provided affected communities with information and awareness on safe hygiene practices, regular handwashing, and the proper use of distributed WASH supplies.</t>
-  </si>
-  <si>
-    <t>One male and one female community volunteer were mobilized to conduct hygiene promotion activities at Sivalaya School and Nilkanda Holding Center in Uttargaya Rural Municipality.</t>
-  </si>
-  <si>
-    <t>A total of 1,328 people were reached with WASH supplies, including buckets, mugs, blankets, hygiene kits, and Peyush (333 sets), in Gosainkunda Rural Municipality–5, covering Sano-Barkhu, Brabal, Thulo-Barkhu, and Thulo-Shyfru. The beneficiaries included 674 males and 654 females.</t>
   </si>
 </sst>
 </file>
@@ -897,6 +871,54 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -986,54 +1008,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,89 +1370,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="2:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="47"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="37" t="s">
+      <c r="J3" s="63"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="71" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:14" s="4" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="29"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
     </row>
     <row r="5" spans="2:14" s="5" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="30"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
     </row>
     <row r="6" spans="2:14" s="5" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
@@ -1499,11 +1473,11 @@
     </row>
     <row r="7" spans="2:14" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="10"/>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="12"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1515,19 +1489,19 @@
       <c r="N7" s="15"/>
     </row>
     <row r="8" spans="2:14" s="19" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="58">
+      <c r="B8" s="27">
         <v>1</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="66" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="30" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="17" t="s">
@@ -1542,13 +1516,13 @@
       <c r="N8" s="18"/>
     </row>
     <row r="9" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B9" s="59"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="67"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="17" t="s">
         <v>16</v>
       </c>
@@ -1561,22 +1535,22 @@
       <c r="N9" s="18"/>
     </row>
     <row r="10" spans="2:14" s="19" customFormat="1" ht="78" x14ac:dyDescent="0.25">
-      <c r="B10" s="58">
+      <c r="B10" s="27">
         <v>2</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="66" t="s">
+      <c r="E10" s="36"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="66" t="s">
+      <c r="I10" s="30" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="17" t="s">
@@ -1590,14 +1564,14 @@
       <c r="N10" s="18"/>
     </row>
     <row r="11" spans="2:14" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="68"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="17" t="s">
         <v>41</v>
       </c>
@@ -1609,14 +1583,14 @@
       <c r="N11" s="18"/>
     </row>
     <row r="12" spans="2:14" s="19" customFormat="1" ht="78" x14ac:dyDescent="0.25">
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="67"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="17" t="s">
         <v>42</v>
       </c>
@@ -1628,14 +1602,14 @@
       <c r="N12" s="18"/>
     </row>
     <row r="13" spans="2:14" s="19" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="66" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="30" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="17" t="s">
@@ -1649,14 +1623,14 @@
       <c r="N13" s="18"/>
     </row>
     <row r="14" spans="2:14" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="17" t="s">
         <v>45</v>
       </c>
@@ -1668,14 +1642,14 @@
       <c r="N14" s="18"/>
     </row>
     <row r="15" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B15" s="59"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
       <c r="J15" s="17" t="s">
         <v>46</v>
       </c>
@@ -1687,22 +1661,22 @@
       <c r="N15" s="18"/>
     </row>
     <row r="16" spans="2:14" s="19" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="58">
+      <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="60" t="s">
+      <c r="D16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="66" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="66" t="s">
+      <c r="I16" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="17" t="s">
@@ -1716,14 +1690,14 @@
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:14" s="19" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="17" t="s">
         <v>48</v>
       </c>
@@ -1735,14 +1709,14 @@
       <c r="N17" s="18"/>
     </row>
     <row r="18" spans="2:14" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="B18" s="68"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1754,14 +1728,14 @@
       <c r="N18" s="18"/>
     </row>
     <row r="19" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="67"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
       <c r="J19" s="17" t="s">
         <v>50</v>
       </c>
@@ -1773,13 +1747,13 @@
       <c r="N19" s="18"/>
     </row>
     <row r="20" spans="2:14" s="19" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="59"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="67"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="17" t="s">
         <v>25</v>
       </c>
@@ -1794,22 +1768,22 @@
       <c r="N20" s="18"/>
     </row>
     <row r="21" spans="2:14" s="19" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="58">
+      <c r="B21" s="27">
         <v>4</v>
       </c>
-      <c r="C21" s="60" t="s">
+      <c r="C21" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="60" t="s">
+      <c r="D21" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="66" t="s">
+      <c r="E21" s="36"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="66" t="s">
+      <c r="I21" s="30" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="17" t="s">
@@ -1823,14 +1797,14 @@
       <c r="N21" s="18"/>
     </row>
     <row r="22" spans="2:14" s="19" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
       <c r="J22" s="17" t="s">
         <v>52</v>
       </c>
@@ -1842,14 +1816,14 @@
       <c r="N22" s="18"/>
     </row>
     <row r="23" spans="2:14" s="19" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="59"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
       <c r="J23" s="17" t="s">
         <v>53</v>
       </c>
@@ -1861,19 +1835,19 @@
       <c r="N23" s="18"/>
     </row>
     <row r="24" spans="2:14" s="19" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="58">
+      <c r="B24" s="27">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="60" t="s">
+      <c r="D24" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="66" t="s">
+      <c r="E24" s="36"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="30" t="s">
         <v>29</v>
       </c>
       <c r="I24" s="17" t="s">
@@ -1890,13 +1864,13 @@
       <c r="N24" s="18"/>
     </row>
     <row r="25" spans="2:14" s="19" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="31"/>
       <c r="I25" s="17" t="s">
         <v>31</v>
       </c>
@@ -1911,13 +1885,13 @@
       <c r="N25" s="18"/>
     </row>
     <row r="26" spans="2:14" s="19" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="59"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="67"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="32"/>
       <c r="I26" s="17" t="s">
         <v>33</v>
       </c>
@@ -1938,6 +1912,42 @@
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="52">
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="H10:H15"/>
     <mergeCell ref="B10:B15"/>
@@ -1954,42 +1964,6 @@
     <mergeCell ref="B16:B20"/>
     <mergeCell ref="D16:D20"/>
     <mergeCell ref="E16:E20"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="G10:G15"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="N3:N5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D7 D27:D1048576" xr:uid="{54404F6C-C21F-4251-B85D-BDF582989099}">
@@ -2025,85 +1999,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="2:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:13" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="37" t="s">
+      <c r="J3" s="64"/>
+      <c r="K3" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="71" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:13" s="4" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="29"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
     </row>
     <row r="5" spans="2:13" s="5" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="30"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
     </row>
     <row r="6" spans="2:13" s="5" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
@@ -2123,11 +2097,11 @@
     </row>
     <row r="7" spans="2:13" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="10"/>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="12"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -2138,19 +2112,19 @@
       <c r="M7" s="15"/>
     </row>
     <row r="8" spans="2:13" s="19" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="58">
+      <c r="B8" s="27">
         <v>1</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="66" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="30" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="17" t="s">
@@ -2162,21 +2136,17 @@
       <c r="K8" s="18">
         <v>4</v>
       </c>
-      <c r="L8" s="18">
-        <v>1</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" s="19" customFormat="1" ht="62.4" x14ac:dyDescent="0.25">
-      <c r="B9" s="59"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="67"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" spans="2:13" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="17" t="s">
         <v>16</v>
       </c>
@@ -2186,27 +2156,23 @@
       <c r="K9" s="18">
         <v>4</v>
       </c>
-      <c r="L9" s="18">
-        <v>3</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>66</v>
-      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
     </row>
     <row r="10" spans="2:13" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="58">
+      <c r="B10" s="27">
         <v>2</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="66" t="s">
+      <c r="E10" s="36"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="30" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="17" t="s">
@@ -2218,21 +2184,17 @@
       <c r="K10" s="18">
         <v>8000</v>
       </c>
-      <c r="L10" s="18">
-        <v>78</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>67</v>
-      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
     </row>
     <row r="11" spans="2:13" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B11" s="59"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="67"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="17" t="s">
         <v>21</v>
       </c>
@@ -2246,19 +2208,19 @@
       <c r="M11" s="18"/>
     </row>
     <row r="12" spans="2:13" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="58">
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="60" t="s">
+      <c r="D12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="66" t="s">
+      <c r="E12" s="36"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="30" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="17" t="s">
@@ -2274,13 +2236,13 @@
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="2:13" s="19" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="59"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="67"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2290,12 +2252,8 @@
       <c r="K13" s="18">
         <v>2120</v>
       </c>
-      <c r="L13" s="18">
-        <v>133</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>68</v>
-      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
     </row>
     <row r="14" spans="2:13" s="19" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="20">
@@ -2322,27 +2280,23 @@
       <c r="K14" s="18">
         <v>5</v>
       </c>
-      <c r="L14" s="18">
-        <v>9</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" s="19" customFormat="1" ht="249.6" x14ac:dyDescent="0.25">
-      <c r="B15" s="58">
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+    </row>
+    <row r="15" spans="2:13" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="B15" s="27">
         <v>5</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="60" t="s">
+      <c r="D15" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="66" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="30" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="17" t="s">
@@ -2354,22 +2308,17 @@
       <c r="K15" s="18">
         <v>10600</v>
       </c>
-      <c r="L15" s="18">
-        <f>1328+48+30</f>
-        <v>1406</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>70</v>
-      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
     </row>
     <row r="16" spans="2:13" s="19" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="68"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="72"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="17" t="s">
         <v>31</v>
       </c>
@@ -2379,21 +2328,17 @@
       <c r="K16" s="18">
         <v>5</v>
       </c>
-      <c r="L16" s="18">
-        <v>2</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>71</v>
-      </c>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
     </row>
     <row r="17" spans="2:13" s="19" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="59"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="67"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="32"/>
       <c r="I17" s="17" t="s">
         <v>33</v>
       </c>
@@ -2403,12 +2348,8 @@
       <c r="K17" s="18">
         <v>4250</v>
       </c>
-      <c r="L17" s="18">
-        <v>1328</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>72</v>
-      </c>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
     </row>
     <row r="20" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
@@ -2462,33 +2403,6 @@
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
@@ -2503,6 +2417,33 @@
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M3:M5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D7 D18:D1048576" xr:uid="{8C659561-7D2B-402D-AEDD-E2CD4035C44E}">

--- a/Chaya_Monitoring Matrix.xlsx
+++ b/Chaya_Monitoring Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive - Chay-Ya Nepal\Desktop\ktm working project\emergency\rasuwa cynn dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF75EE87-99EC-43D8-90A7-0EF6239A8299}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{0852B150-3F40-4BB5-A447-6A23EDAC7EC4}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{DF75EE87-99EC-43D8-90A7-0EF6239A8299}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{027D72C8-2ABC-41BD-9162-82793D6F4E4B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{337F1315-C639-4669-8235-F9C229A04F9D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="68">
   <si>
     <t>Disaster Response Matrix - 2025</t>
   </si>
@@ -328,6 +328,34 @@
   </si>
   <si>
     <t># of children benefited</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CCC W5. Hygiene promotion and community engagement for behaviour and social change</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+At-risk and affected populations have timely access to culturally appropriate, gender- and age-sensitive information, services and interventions related to hygiene promotion, and adopt safe hygiene practices</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kalika-2 (Gumba )- 2 temporary toilets, 2 handwashing stations, 1,000L HDPE tank &amp;  Uttargaya-5 (Nilkantha)- 2 toilets, 2 handwashing stations, 300L tank</t>
+  </si>
+  <si>
+    <t>Uttargaya (47HHs) &amp; Gosaikunda (900 HHs)</t>
   </si>
 </sst>
 </file>
@@ -871,143 +899,143 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,89 +1398,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
     </row>
     <row r="2" spans="2:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="53" t="s">
+      <c r="J3" s="47"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="71" t="s">
+      <c r="M3" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="55" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:14" s="4" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="45"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
     </row>
     <row r="5" spans="2:14" s="5" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="46"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
     </row>
     <row r="6" spans="2:14" s="5" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
@@ -1473,11 +1501,11 @@
     </row>
     <row r="7" spans="2:14" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="10"/>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="12"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1489,19 +1517,19 @@
       <c r="N7" s="15"/>
     </row>
     <row r="8" spans="2:14" s="19" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27">
+      <c r="B8" s="58">
         <v>1</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="30" t="s">
+      <c r="E8" s="62"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="64" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="17" t="s">
@@ -1516,13 +1544,13 @@
       <c r="N8" s="18"/>
     </row>
     <row r="9" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="32"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="66"/>
       <c r="I9" s="17" t="s">
         <v>16</v>
       </c>
@@ -1535,22 +1563,22 @@
       <c r="N9" s="18"/>
     </row>
     <row r="10" spans="2:14" s="19" customFormat="1" ht="78" x14ac:dyDescent="0.25">
-      <c r="B10" s="27">
+      <c r="B10" s="58">
         <v>2</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="30" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="64" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="17" t="s">
@@ -1564,14 +1592,14 @@
       <c r="N10" s="18"/>
     </row>
     <row r="11" spans="2:14" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
       <c r="J11" s="17" t="s">
         <v>41</v>
       </c>
@@ -1583,14 +1611,14 @@
       <c r="N11" s="18"/>
     </row>
     <row r="12" spans="2:14" s="19" customFormat="1" ht="78" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="32"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="66"/>
       <c r="J12" s="17" t="s">
         <v>42</v>
       </c>
@@ -1602,14 +1630,14 @@
       <c r="N12" s="18"/>
     </row>
     <row r="13" spans="2:14" s="19" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="28"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="30" t="s">
+      <c r="B13" s="72"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="64" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="17" t="s">
@@ -1623,14 +1651,14 @@
       <c r="N13" s="18"/>
     </row>
     <row r="14" spans="2:14" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="B14" s="28"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
       <c r="J14" s="17" t="s">
         <v>45</v>
       </c>
@@ -1642,14 +1670,14 @@
       <c r="N14" s="18"/>
     </row>
     <row r="15" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B15" s="29"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
       <c r="J15" s="17" t="s">
         <v>46</v>
       </c>
@@ -1661,22 +1689,22 @@
       <c r="N15" s="18"/>
     </row>
     <row r="16" spans="2:14" s="19" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27">
+      <c r="B16" s="58">
         <v>3</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="30" t="s">
+      <c r="E16" s="62"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="17" t="s">
@@ -1690,14 +1718,14 @@
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="2:14" s="19" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="28"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
       <c r="J17" s="17" t="s">
         <v>48</v>
       </c>
@@ -1709,14 +1737,14 @@
       <c r="N17" s="18"/>
     </row>
     <row r="18" spans="2:14" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
       <c r="J18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1728,14 +1756,14 @@
       <c r="N18" s="18"/>
     </row>
     <row r="19" spans="2:14" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B19" s="28"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
       <c r="J19" s="17" t="s">
         <v>50</v>
       </c>
@@ -1747,13 +1775,13 @@
       <c r="N19" s="18"/>
     </row>
     <row r="20" spans="2:14" s="19" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="29"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="32"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="66"/>
       <c r="I20" s="17" t="s">
         <v>25</v>
       </c>
@@ -1768,22 +1796,22 @@
       <c r="N20" s="18"/>
     </row>
     <row r="21" spans="2:14" s="19" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27">
+      <c r="B21" s="58">
         <v>4</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="30" t="s">
+      <c r="E21" s="62"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="30" t="s">
+      <c r="I21" s="64" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="17" t="s">
@@ -1797,14 +1825,14 @@
       <c r="N21" s="18"/>
     </row>
     <row r="22" spans="2:14" s="19" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="28"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
       <c r="J22" s="17" t="s">
         <v>52</v>
       </c>
@@ -1816,14 +1844,14 @@
       <c r="N22" s="18"/>
     </row>
     <row r="23" spans="2:14" s="19" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="29"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
       <c r="J23" s="17" t="s">
         <v>53</v>
       </c>
@@ -1835,19 +1863,19 @@
       <c r="N23" s="18"/>
     </row>
     <row r="24" spans="2:14" s="19" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="27">
+      <c r="B24" s="58">
         <v>5</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="30" t="s">
+      <c r="E24" s="62"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="64" t="s">
         <v>29</v>
       </c>
       <c r="I24" s="17" t="s">
@@ -1864,13 +1892,13 @@
       <c r="N24" s="18"/>
     </row>
     <row r="25" spans="2:14" s="19" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="28"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="31"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="65"/>
       <c r="I25" s="17" t="s">
         <v>31</v>
       </c>
@@ -1885,13 +1913,13 @@
       <c r="N25" s="18"/>
     </row>
     <row r="26" spans="2:14" s="19" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="29"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="32"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="66"/>
       <c r="I26" s="17" t="s">
         <v>33</v>
       </c>
@@ -1912,6 +1940,46 @@
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="52">
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="H10:H15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
     <mergeCell ref="B1:N1"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
@@ -1924,46 +1992,6 @@
     <mergeCell ref="L3:L5"/>
     <mergeCell ref="M3:M5"/>
     <mergeCell ref="N3:N5"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="G10:G15"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="H10:H15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="I16:I19"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="B16:B20"/>
-    <mergeCell ref="D16:D20"/>
-    <mergeCell ref="E16:E20"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D7 D27:D1048576" xr:uid="{54404F6C-C21F-4251-B85D-BDF582989099}">
@@ -1999,85 +2027,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
     </row>
     <row r="2" spans="2:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:13" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="64"/>
-      <c r="K3" s="53" t="s">
+      <c r="J3" s="48"/>
+      <c r="K3" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="71" t="s">
+      <c r="L3" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="71" t="s">
+      <c r="M3" s="55" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:13" s="4" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="45"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
     </row>
     <row r="5" spans="2:13" s="5" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="46"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
     </row>
     <row r="6" spans="2:13" s="5" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
@@ -2097,11 +2125,11 @@
     </row>
     <row r="7" spans="2:13" s="16" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="10"/>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="12"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -2112,19 +2140,19 @@
       <c r="M7" s="15"/>
     </row>
     <row r="8" spans="2:13" s="19" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27">
+      <c r="B8" s="58">
         <v>1</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="30" t="s">
+      <c r="E8" s="62"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="64" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="17" t="s">
@@ -2140,13 +2168,13 @@
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="2:13" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="32"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="66"/>
       <c r="I9" s="17" t="s">
         <v>16</v>
       </c>
@@ -2160,19 +2188,19 @@
       <c r="M9" s="18"/>
     </row>
     <row r="10" spans="2:13" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="27">
+      <c r="B10" s="58">
         <v>2</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="30" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="64" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="17" t="s">
@@ -2188,13 +2216,13 @@
       <c r="M10" s="18"/>
     </row>
     <row r="11" spans="2:13" s="19" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="32"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="66"/>
       <c r="I11" s="17" t="s">
         <v>21</v>
       </c>
@@ -2208,19 +2236,19 @@
       <c r="M11" s="18"/>
     </row>
     <row r="12" spans="2:13" s="19" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="27">
+      <c r="B12" s="58">
         <v>3</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="30" t="s">
+      <c r="E12" s="62"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="64" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="17" t="s">
@@ -2236,13 +2264,13 @@
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="2:13" s="19" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="32"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="66"/>
       <c r="I13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2280,24 +2308,28 @@
       <c r="K14" s="18">
         <v>5</v>
       </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="L14" s="18">
+        <v>2</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="2:13" s="19" customFormat="1" ht="46.8" x14ac:dyDescent="0.25">
-      <c r="B15" s="27">
+      <c r="B15" s="58">
         <v>5</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="30" t="s">
-        <v>29</v>
+      <c r="E15" s="62"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="64" t="s">
+        <v>65</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>30</v>
@@ -2312,13 +2344,13 @@
       <c r="M15" s="18"/>
     </row>
     <row r="16" spans="2:13" s="19" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="28"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="31"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="65"/>
       <c r="I16" s="17" t="s">
         <v>31</v>
       </c>
@@ -2332,13 +2364,13 @@
       <c r="M16" s="18"/>
     </row>
     <row r="17" spans="2:13" s="19" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="29"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="32"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="66"/>
       <c r="I17" s="17" t="s">
         <v>33</v>
       </c>
@@ -2348,8 +2380,12 @@
       <c r="K17" s="18">
         <v>4250</v>
       </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
+      <c r="L17" s="18">
+        <v>4065</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="20" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
@@ -2403,6 +2439,33 @@
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
@@ -2417,33 +2480,6 @@
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D7 D18:D1048576" xr:uid="{8C659561-7D2B-402D-AEDD-E2CD4035C44E}">
